--- a/report/loss/calc-walkthrough/loss-calculation-walkthrough.xlsx
+++ b/report/loss/calc-walkthrough/loss-calculation-walkthrough.xlsx
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>20848030.67711663</v>
+        <v>20869279.22072987</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1658,13 +1658,13 @@
         <v>0</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U21" s="7" t="n">
         <v>42</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22">
@@ -1677,13 +1677,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U22" s="7" t="n">
         <v>13</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="S37" s="13" t="n">
-        <v>1227520.553842015</v>
+        <v>1248769.097455249</v>
       </c>
     </row>
     <row r="38">
@@ -2227,7 +2227,7 @@
         <v/>
       </c>
       <c r="I15" s="22" t="n">
-        <v>41239.66901756078</v>
+        <v>62488.21263079525</v>
       </c>
       <c r="J15" s="21">
         <f>MIN(I15,H15)</f>
@@ -3416,17 +3416,17 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0.75</v>
+        <v>2.75</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>6.63081310834806</v>
+        <v>8.159218973584622</v>
       </c>
       <c r="K6" s="29" t="n">
-        <v>6050.552538873999</v>
+        <v>27299.09615210847</v>
       </c>
       <c r="L6" s="29" t="n">
         <v>0</v>
